--- a/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/std/results.xlsx
+++ b/experiments/results/mobilenetv2_imagenet/ImageNet-1K/DICE/adaptive/std/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -799,6 +799,80 @@
       <c r="K12" s="4" t="inlineStr">
         <is>
           <t>dice_p=50,ash_p=None,react_th=None,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>91.29000000000001</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>87.03</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>95.40000000000001</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>93.25</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>91.73999999999999</v>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=0.1,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>37.02</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>91.09</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>86.86</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>95.09999999999999</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>36.25</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>93.05</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=10,ash_p=None,react_th=None,scale_th=0.05,type=std</t>
         </is>
       </c>
     </row>
